--- a/SHET/perechen.xlsx
+++ b/SHET/perechen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WWWW\protocols\SHET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA039441-5977-44A7-9841-F09BC95D7703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F788568-4F7E-43CB-8B95-0B045113CED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -392,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" customWidth="1"/>
@@ -576,8 +576,112 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
     </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>9</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="51">
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="E27:E29"/>
+    <mergeCell ref="F27:F29"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="F24:F26"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="A12:A14"/>
     <mergeCell ref="D18:D20"/>
     <mergeCell ref="E3:E5"/>
     <mergeCell ref="F3:F5"/>
@@ -594,26 +698,6 @@
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="D9:D11"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="A12:A14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
